--- a/data/trans_bre/P1409-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1409-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-3,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-62,12%</t>
+          <t>-58,52%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,35</t>
+          <t>-2,17; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,53</t>
+          <t>-1,6; 4,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 0,59</t>
+          <t>-9,19; 0,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 127,34</t>
+          <t>-54,64; 122,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 181,36</t>
+          <t>-31,76; 160,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-92,1; 80,59</t>
+          <t>-90,71; 56,79</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,47</t>
+          <t>-1,99</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>159,65%</t>
+          <t>-32,42%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,58</t>
+          <t>-0,16; 3,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,25</t>
+          <t>-1,06; 2,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 44,09</t>
+          <t>-5,35; 0,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 275,31</t>
+          <t>-10,37; 275,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 184,23</t>
+          <t>-33,1; 149,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 1030,78</t>
+          <t>-65,42; 22,99</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,62</t>
+          <t>-0,3; 2,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,36</t>
+          <t>-0,28; 3,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,11</t>
+          <t>-1,8; 2,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 352,14</t>
+          <t>-20,68; 357,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 321,05</t>
+          <t>-16,69; 298,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 113,24</t>
+          <t>-34,41; 102,12</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>147,06%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,39</t>
+          <t>-0,74; 2,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,86</t>
+          <t>0,44; 3,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,27</t>
+          <t>0,73; 4,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,15; 556,93</t>
+          <t>-58,76; 657,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 650,03</t>
+          <t>1,54; 535,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,44; 469,13</t>
+          <t>14,57; 216,72</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,88</t>
+          <t>-0,1; 3,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,68</t>
+          <t>-1,31; 3,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,53</t>
+          <t>0,09; 3,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 738,88</t>
+          <t>-18,87; 895,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 270,08</t>
+          <t>-38,35; 236,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 187,36</t>
+          <t>2,36; 205,97</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,6</t>
+          <t>-4,02; 1,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,91</t>
+          <t>0,05; 4,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,28</t>
+          <t>0,02; 3,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,49; 101,82</t>
+          <t>-74,94; 98,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 630,92</t>
+          <t>-10,24; 586,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,83; 92,21</t>
+          <t>-0,18; 214,49</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>102,96%</t>
+          <t>104,23%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,46</t>
+          <t>-2,99; 2,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 3,03</t>
+          <t>-4,49; 2,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,42</t>
+          <t>0,82; 5,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-63,43; 177,14</t>
+          <t>-68,29; 167,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-60,62; 76,93</t>
+          <t>-59,9; 72,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,3; 271,29</t>
+          <t>14,13; 295,52</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,6</t>
+          <t>0,1; 1,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,28</t>
+          <t>0,64; 2,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 9,9</t>
+          <t>-0,1; 1,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,37; 98,72</t>
+          <t>3,94; 102,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,26; 102,86</t>
+          <t>20,53; 112,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,06; 282,19</t>
+          <t>-2,36; 53,82</t>
         </is>
       </c>
     </row>
